--- a/bank_data.xlsx
+++ b/bank_data.xlsx
@@ -5,93 +5,79 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/balaiah/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/balaiah/Documents/Agenti-AI-3.0/bank-assistant/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C722C7FD-03F4-B44E-809A-239DCA284522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E5292AE-E04A-A14E-A7A0-94E6A6F32170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17460" activeTab="1" xr2:uid="{B5E11FFE-54E7-FF4D-B679-A776388999DA}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Salary" sheetId="1" r:id="rId1"/>
     <sheet name="Expenses" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>Date</t>
   </si>
   <si>
+    <t>Category</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>Swiggy</t>
+  </si>
+  <si>
+    <t>Shopping</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>Uber</t>
+  </si>
+  <si>
+    <t>restaurant</t>
+  </si>
+  <si>
+    <t>today expense</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
     <t>Salary</t>
   </si>
   <si>
-    <t>Amount</t>
-  </si>
-  <si>
     <t>Bonus</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Food</t>
-  </si>
-  <si>
-    <t>Swiggy</t>
-  </si>
-  <si>
-    <t>Shopping</t>
-  </si>
-  <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>Travel</t>
-  </si>
-  <si>
-    <t>Uber</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -122,8 +108,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,7 +443,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20FB526-389D-C641-92AB-BCF577CE9499}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -466,7 +452,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
@@ -477,7 +463,7 @@
         <v>46204</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>200000</v>
@@ -488,7 +474,7 @@
         <v>46218</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>10000</v>
@@ -500,67 +486,98 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C09923B7-8CD5-FD43-8A03-FB93392D1EBC}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>46205</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
-        <v>46205</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
       </c>
       <c r="D2">
         <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>46206</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>2500</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>46208</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>450</v>
       </c>
     </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>45367</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>50000</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>